--- a/Team-Data/2012-13/4-2-2012-13.xlsx
+++ b/Team-Data/2012-13/4-2-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -745,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
         <v>11</v>
@@ -787,7 +854,7 @@
         <v>10</v>
       </c>
       <c r="AT2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
@@ -805,7 +872,7 @@
         <v>7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA2" t="n">
         <v>26</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -921,16 +988,16 @@
         <v>-0.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF3" t="n">
         <v>14</v>
       </c>
       <c r="AG3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
@@ -954,13 +1021,13 @@
         <v>17</v>
       </c>
       <c r="AO3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP3" t="n">
         <v>20</v>
       </c>
-      <c r="AP3" t="n">
-        <v>19</v>
-      </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
         <v>29</v>
@@ -972,7 +1039,7 @@
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV3" t="n">
         <v>13</v>
@@ -990,7 +1057,7 @@
         <v>26</v>
       </c>
       <c r="BA3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB3" t="n">
         <v>18</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>1.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
@@ -1148,7 +1215,7 @@
         <v>5</v>
       </c>
       <c r="AS4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
@@ -1160,7 +1227,7 @@
         <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX4" t="n">
         <v>18</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-9.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E6" t="n">
         <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>0.548</v>
+        <v>0.556</v>
       </c>
       <c r="H6" t="n">
         <v>48.3</v>
@@ -1407,7 +1474,7 @@
         <v>35.7</v>
       </c>
       <c r="J6" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K6" t="n">
         <v>0.436</v>
@@ -1416,19 +1483,19 @@
         <v>5.1</v>
       </c>
       <c r="M6" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0.342</v>
+        <v>0.345</v>
       </c>
       <c r="O6" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P6" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.776</v>
+        <v>0.777</v>
       </c>
       <c r="R6" t="n">
         <v>12.8</v>
@@ -1440,16 +1507,16 @@
         <v>43.4</v>
       </c>
       <c r="U6" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V6" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W6" t="n">
         <v>7.3</v>
       </c>
       <c r="X6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y6" t="n">
         <v>5.9</v>
@@ -1458,25 +1525,25 @@
         <v>19.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="AC6" t="n">
         <v>0.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
         <v>15</v>
@@ -1485,7 +1552,7 @@
         <v>26</v>
       </c>
       <c r="AJ6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK6" t="n">
         <v>27</v>
@@ -1500,13 +1567,13 @@
         <v>24</v>
       </c>
       <c r="AO6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR6" t="n">
         <v>6</v>
@@ -1521,22 +1588,22 @@
         <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AZ6" t="n">
         <v>11</v>
       </c>
       <c r="BA6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB6" t="n">
         <v>30</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE7" t="n">
         <v>28</v>
@@ -1697,7 +1764,7 @@
         <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU7" t="n">
         <v>25</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -1753,19 +1820,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E8" t="n">
         <v>36</v>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G8" t="n">
-        <v>0.486</v>
+        <v>0.493</v>
       </c>
       <c r="H8" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I8" t="n">
         <v>38.6</v>
@@ -1774,7 +1841,7 @@
         <v>83.8</v>
       </c>
       <c r="K8" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L8" t="n">
         <v>7.5</v>
@@ -1786,22 +1853,22 @@
         <v>0.373</v>
       </c>
       <c r="O8" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="P8" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.791</v>
+        <v>0.794</v>
       </c>
       <c r="R8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T8" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U8" t="n">
         <v>23</v>
@@ -1822,25 +1889,25 @@
         <v>20.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>101.1</v>
+        <v>101.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
         <v>17</v>
       </c>
       <c r="AF8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH8" t="n">
         <v>3</v>
@@ -1861,22 +1928,22 @@
         <v>12</v>
       </c>
       <c r="AN8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP8" t="n">
         <v>24</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR8" t="n">
         <v>26</v>
       </c>
       <c r="AS8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
         <v>16</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>4.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
@@ -2025,7 +2092,7 @@
         <v>4</v>
       </c>
       <c r="AH9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2067,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW9" t="n">
         <v>2</v>
@@ -2079,7 +2146,7 @@
         <v>28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
         <v>4</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>0.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
@@ -2416,7 +2483,7 @@
         <v>17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR11" t="n">
         <v>23</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -2559,16 +2626,16 @@
         <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE12" t="n">
         <v>12</v>
       </c>
       <c r="AF12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
         <v>24</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2817,7 @@
         <v>8</v>
       </c>
       <c r="AG13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH13" t="n">
         <v>14</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -2935,7 +3002,7 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI14" t="n">
         <v>6</v>
@@ -2956,7 +3023,7 @@
         <v>21</v>
       </c>
       <c r="AO14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP14" t="n">
         <v>9</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -3027,22 +3094,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F15" t="n">
         <v>36</v>
       </c>
       <c r="G15" t="n">
-        <v>0.52</v>
+        <v>0.514</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J15" t="n">
         <v>81.3</v>
@@ -3060,7 +3127,7 @@
         <v>0.358</v>
       </c>
       <c r="O15" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="P15" t="n">
         <v>27.7</v>
@@ -3069,13 +3136,13 @@
         <v>0.6879999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S15" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="T15" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="U15" t="n">
         <v>22.1</v>
@@ -3099,28 +3166,28 @@
         <v>22.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.3</v>
+        <v>102.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF15" t="n">
         <v>14</v>
       </c>
       <c r="AG15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH15" t="n">
         <v>28</v>
       </c>
       <c r="AI15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ15" t="n">
         <v>18</v>
@@ -3150,7 +3217,7 @@
         <v>13</v>
       </c>
       <c r="AS15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT15" t="n">
         <v>3</v>
@@ -3162,7 +3229,7 @@
         <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX15" t="n">
         <v>15</v>
@@ -3171,7 +3238,7 @@
         <v>16</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3305,10 +3372,10 @@
         <v>21</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3320,10 +3387,10 @@
         <v>23</v>
       </c>
       <c r="AO16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ16" t="n">
         <v>6</v>
@@ -3362,7 +3429,7 @@
         <v>26</v>
       </c>
       <c r="BC16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -3391,25 +3458,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E17" t="n">
         <v>58</v>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>0.784</v>
+        <v>0.795</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
       </c>
       <c r="I17" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J17" t="n">
-        <v>77.7</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K17" t="n">
         <v>0.497</v>
@@ -3424,34 +3491,34 @@
         <v>0.394</v>
       </c>
       <c r="O17" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P17" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="R17" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>30</v>
       </c>
       <c r="T17" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="U17" t="n">
         <v>22.9</v>
       </c>
       <c r="V17" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="W17" t="n">
         <v>8.9</v>
       </c>
       <c r="X17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y17" t="n">
         <v>3.3</v>
@@ -3460,16 +3527,16 @@
         <v>18.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>103.1</v>
+        <v>103.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3514,13 +3581,13 @@
         <v>28</v>
       </c>
       <c r="AS17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV17" t="n">
         <v>3</v>
@@ -3529,7 +3596,7 @@
         <v>3</v>
       </c>
       <c r="AX17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3538,7 +3605,7 @@
         <v>8</v>
       </c>
       <c r="BA17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB17" t="n">
         <v>5</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-1.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
         <v>17</v>
@@ -3663,7 +3730,7 @@
         <v>17</v>
       </c>
       <c r="AH18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI18" t="n">
         <v>5</v>
@@ -3714,7 +3781,7 @@
         <v>2</v>
       </c>
       <c r="AY18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ18" t="n">
         <v>9</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -3833,16 +3900,16 @@
         <v>-2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF19" t="n">
         <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH19" t="n">
         <v>26</v>
@@ -3851,7 +3918,7 @@
         <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3896,7 +3963,7 @@
         <v>18</v>
       </c>
       <c r="AY19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ19" t="n">
         <v>6</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-3.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE20" t="n">
         <v>25</v>
@@ -4039,7 +4106,7 @@
         <v>13</v>
       </c>
       <c r="AL20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM20" t="n">
         <v>21</v>
@@ -4060,7 +4127,7 @@
         <v>12</v>
       </c>
       <c r="AS20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT20" t="n">
         <v>18</v>
@@ -4069,7 +4136,7 @@
         <v>22</v>
       </c>
       <c r="AV20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW20" t="n">
         <v>29</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E21" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F21" t="n">
         <v>26</v>
       </c>
       <c r="G21" t="n">
-        <v>0.644</v>
+        <v>0.639</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
@@ -4137,10 +4204,10 @@
         <v>36.1</v>
       </c>
       <c r="J21" t="n">
-        <v>81</v>
+        <v>81.2</v>
       </c>
       <c r="K21" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L21" t="n">
         <v>10.7</v>
@@ -4149,7 +4216,7 @@
         <v>28.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0.374</v>
+        <v>0.372</v>
       </c>
       <c r="O21" t="n">
         <v>16.6</v>
@@ -4158,16 +4225,16 @@
         <v>21.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.759</v>
+        <v>0.76</v>
       </c>
       <c r="R21" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S21" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T21" t="n">
-        <v>40.5</v>
+        <v>40.7</v>
       </c>
       <c r="U21" t="n">
         <v>19.2</v>
@@ -4182,22 +4249,22 @@
         <v>3.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="n">
         <v>19.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AE21" t="n">
         <v>8</v>
@@ -4206,7 +4273,7 @@
         <v>6</v>
       </c>
       <c r="AG21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH21" t="n">
         <v>30</v>
@@ -4218,7 +4285,7 @@
         <v>20</v>
       </c>
       <c r="AK21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4227,10 +4294,10 @@
         <v>2</v>
       </c>
       <c r="AN21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP21" t="n">
         <v>16</v>
@@ -4239,13 +4306,13 @@
         <v>14</v>
       </c>
       <c r="AR21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT21" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AU21" t="n">
         <v>29</v>
@@ -4272,7 +4339,7 @@
         <v>11</v>
       </c>
       <c r="BC21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4424,10 +4491,10 @@
         <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU22" t="n">
         <v>21</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4682,7 @@
         <v>10</v>
       </c>
       <c r="AV23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4800,7 +4867,7 @@
         <v>2</v>
       </c>
       <c r="AW24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX24" t="n">
         <v>17</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-6.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE25" t="n">
         <v>27</v>
@@ -4985,7 +5052,7 @@
         <v>15</v>
       </c>
       <c r="AX25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY25" t="n">
         <v>17</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5119,13 +5186,13 @@
         <v>19</v>
       </c>
       <c r="AH26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI26" t="n">
         <v>17</v>
       </c>
       <c r="AJ26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK26" t="n">
         <v>14</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -5289,10 +5356,10 @@
         <v>-4.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF27" t="n">
         <v>23</v>
@@ -5337,7 +5404,7 @@
         <v>28</v>
       </c>
       <c r="AT27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU27" t="n">
         <v>26</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>7.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5483,7 +5550,7 @@
         <v>2</v>
       </c>
       <c r="AH28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -5653,10 +5720,10 @@
         <v>-2.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF29" t="n">
         <v>23</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5917,7 @@
         <v>7</v>
       </c>
       <c r="AI30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ30" t="n">
         <v>11</v>
@@ -5865,7 +5932,7 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO30" t="n">
         <v>7</v>
@@ -5898,13 +5965,13 @@
         <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ30" t="n">
         <v>29</v>
       </c>
       <c r="BA30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB30" t="n">
         <v>13</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
@@ -5939,25 +6006,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F31" t="n">
         <v>46</v>
       </c>
       <c r="G31" t="n">
-        <v>0.378</v>
+        <v>0.37</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="J31" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K31" t="n">
         <v>0.434</v>
@@ -5966,28 +6033,28 @@
         <v>6.7</v>
       </c>
       <c r="M31" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.365</v>
+        <v>0.364</v>
       </c>
       <c r="O31" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="P31" t="n">
         <v>21.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.735</v>
+        <v>0.736</v>
       </c>
       <c r="R31" t="n">
         <v>10.9</v>
       </c>
       <c r="S31" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T31" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="U31" t="n">
         <v>21.9</v>
@@ -6005,19 +6072,19 @@
         <v>4.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AB31" t="n">
-        <v>93.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>-2.2</v>
+        <v>-2.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AE31" t="n">
         <v>21</v>
@@ -6029,13 +6096,13 @@
         <v>21</v>
       </c>
       <c r="AH31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI31" t="n">
         <v>28</v>
       </c>
       <c r="AJ31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AK31" t="n">
         <v>29</v>
@@ -6047,7 +6114,7 @@
         <v>20</v>
       </c>
       <c r="AN31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO31" t="n">
         <v>25</v>
@@ -6059,19 +6126,19 @@
         <v>21</v>
       </c>
       <c r="AR31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU31" t="n">
         <v>18</v>
       </c>
       <c r="AV31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW31" t="n">
         <v>22</v>
@@ -6080,10 +6147,10 @@
         <v>24</v>
       </c>
       <c r="AY31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA31" t="n">
         <v>24</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-2-2012-13</t>
+          <t>2013-04-02</t>
         </is>
       </c>
     </row>
